--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\portfolio-notebooks\public\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F059B1-3B72-4EE3-B9AF-472EF2027C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592484DD-A023-4EC3-8FD9-851685F367C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,15 +243,9 @@
     <t>weekly</t>
   </si>
   <si>
-    <t>portfolio_sheet</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>assets_file</t>
-  </si>
-  <si>
     <t>start</t>
   </si>
   <si>
@@ -339,13 +333,19 @@
     <t>F_DIGRS</t>
   </si>
   <si>
-    <t>assets.xlsx</t>
-  </si>
-  <si>
-    <t>indices.xlsx</t>
-  </si>
-  <si>
-    <t>currencies.xlsx</t>
+    <t>portfolios_source</t>
+  </si>
+  <si>
+    <t>assets_source</t>
+  </si>
+  <si>
+    <t>assets.xlsx!Main</t>
+  </si>
+  <si>
+    <t>indices.xlsx!Main</t>
+  </si>
+  <si>
+    <t>currencies.xlsx!Main</t>
   </si>
 </sst>
 </file>
@@ -710,23 +710,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B3" s="6">
         <v>36892</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6">
         <v>46113</v>
@@ -742,39 +742,39 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
         <v>99</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
         <v>100</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
         <v>101</v>
@@ -819,7 +819,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -849,7 +849,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -957,7 +957,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1167,10 +1167,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -1592,10 +1592,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>57</v>

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592484DD-A023-4EC3-8FD9-851685F367C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDCD748-E087-4B51-A3B0-306C855BEB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,12 +333,6 @@
     <t>F_DIGRS</t>
   </si>
   <si>
-    <t>portfolios_source</t>
-  </si>
-  <si>
-    <t>assets_source</t>
-  </si>
-  <si>
     <t>assets.xlsx!Main</t>
   </si>
   <si>
@@ -346,6 +340,12 @@
   </si>
   <si>
     <t>currencies.xlsx!Main</t>
+  </si>
+  <si>
+    <t>portfolios</t>
+  </si>
+  <si>
+    <t>assets</t>
   </si>
 </sst>
 </file>
@@ -704,8 +704,8 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.3828125" customWidth="1"/>
-    <col min="2" max="2" width="17.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -742,7 +742,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
@@ -774,26 +774,26 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
         <v>98</v>
-      </c>
-      <c r="B10" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDCD748-E087-4B51-A3B0-306C855BEB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E65717-849D-4D5E-9DBF-849D2FFBB388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,19 +333,19 @@
     <t>F_DIGRS</t>
   </si>
   <si>
-    <t>assets.xlsx!Main</t>
-  </si>
-  <si>
-    <t>indices.xlsx!Main</t>
-  </si>
-  <si>
-    <t>currencies.xlsx!Main</t>
-  </si>
-  <si>
     <t>portfolios</t>
   </si>
   <si>
     <t>assets</t>
+  </si>
+  <si>
+    <t>assets.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>indices.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>currencies.xlsx!Assets</t>
   </si>
 </sst>
 </file>
@@ -742,7 +742,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
@@ -758,7 +758,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
@@ -766,7 +766,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
         <v>80</v>
@@ -774,26 +774,26 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" t="s">
         <v>101</v>
-      </c>
-      <c r="B11" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\portfolio-notebooks\public\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F059B1-3B72-4EE3-B9AF-472EF2027C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E65717-849D-4D5E-9DBF-849D2FFBB388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,15 +243,9 @@
     <t>weekly</t>
   </si>
   <si>
-    <t>portfolio_sheet</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
-    <t>assets_file</t>
-  </si>
-  <si>
     <t>start</t>
   </si>
   <si>
@@ -339,13 +333,19 @@
     <t>F_DIGRS</t>
   </si>
   <si>
-    <t>assets.xlsx</t>
-  </si>
-  <si>
-    <t>indices.xlsx</t>
-  </si>
-  <si>
-    <t>currencies.xlsx</t>
+    <t>portfolios</t>
+  </si>
+  <si>
+    <t>assets</t>
+  </si>
+  <si>
+    <t>assets.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>indices.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>currencies.xlsx!Assets</t>
   </si>
 </sst>
 </file>
@@ -704,29 +704,29 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.3828125" customWidth="1"/>
-    <col min="2" max="2" width="17.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B3" s="6">
         <v>36892</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6">
         <v>46113</v>
@@ -742,39 +742,39 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
         <v>99</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
         <v>100</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
         <v>101</v>
@@ -819,7 +819,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -849,7 +849,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -929,7 +929,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
@@ -957,7 +957,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1167,10 +1167,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -1592,10 +1592,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>57</v>

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E65717-849D-4D5E-9DBF-849D2FFBB388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFEBACC-DFA3-48EF-B107-2515E3C80EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="7" r:id="rId1"/>
@@ -225,9 +225,6 @@
     <t>MSCI World Enhanced Value Index (USD) Index</t>
   </si>
   <si>
-    <t>__rb_run</t>
-  </si>
-  <si>
     <t>__rb_type</t>
   </si>
   <si>
@@ -346,6 +343,9 @@
   </si>
   <si>
     <t>currencies.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>__rb_check</t>
   </si>
 </sst>
 </file>
@@ -710,23 +710,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" s="6">
         <v>36892</v>
@@ -734,7 +734,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="6">
         <v>46113</v>
@@ -742,58 +742,58 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s">
         <v>98</v>
-      </c>
-      <c r="B9" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -819,12 +819,12 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
@@ -849,7 +849,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -929,25 +929,25 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -957,7 +957,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
@@ -968,7 +968,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
         <v>37</v>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
@@ -1167,34 +1167,34 @@
         <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1400,7 +1400,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
         <v>38</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -1592,10 +1592,10 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>57</v>
@@ -1603,17 +1603,17 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFEBACC-DFA3-48EF-B107-2515E3C80EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1422E242-0151-43AC-B34B-F6FBDDBBE91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="7" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>__rb_check</t>
+  </si>
+  <si>
+    <t>_portfolios</t>
   </si>
 </sst>
 </file>
@@ -766,7 +769,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F61E0B-4D66-46FD-8C68-DD6531582DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFBDE4F-5590-4762-A63B-3D1E81E132AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="108">
   <si>
     <t>Name</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>__leverage</t>
+  </si>
+  <si>
+    <t>AW Grund (1,37)</t>
   </si>
 </sst>
 </file>
@@ -824,7 +827,8 @@
   <cols>
     <col min="1" max="1" width="10.84375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.921875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -838,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>18</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -850,7 +854,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">

--- a/public/example/main.xlsx
+++ b/public/example/main.xlsx
@@ -1,63 +1,287 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\github\jonaskello\backcel\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1422E242-0151-43AC-B34B-F6FBDDBBE91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFBDE4F-5590-4762-A63B-3D1E81E132AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="7" r:id="rId1"/>
-    <sheet name="AW_Grund" sheetId="10" r:id="rId2"/>
-    <sheet name="AW_Mellan" sheetId="11" r:id="rId3"/>
-    <sheet name="AW_Avancerad" sheetId="9" r:id="rId4"/>
-    <sheet name="Benchmarks" sheetId="4" r:id="rId5"/>
+    <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="AW_Grund" sheetId="2" r:id="rId2"/>
+    <sheet name="AW_Mellan" sheetId="3" r:id="rId3"/>
+    <sheet name="AW_Avancerad" sheetId="4" r:id="rId4"/>
+    <sheet name="Benchmarks" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="108">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>portfolios</t>
+  </si>
+  <si>
+    <t>AW_Avancerad</t>
+  </si>
+  <si>
+    <t>AW_Grund</t>
+  </si>
+  <si>
+    <t>AW_Mellan</t>
+  </si>
+  <si>
+    <t>_portfolios</t>
+  </si>
+  <si>
+    <t>Benchmarks</t>
+  </si>
+  <si>
+    <t>assets</t>
+  </si>
+  <si>
+    <t>assets.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>indices.xlsx!Assets</t>
+  </si>
+  <si>
+    <t>currencies.xlsx!Assets</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
   <si>
+    <t>_Name</t>
+  </si>
+  <si>
+    <t>AW Grund</t>
+  </si>
+  <si>
+    <t>__check</t>
+  </si>
+  <si>
+    <t>half-year</t>
+  </si>
+  <si>
+    <t>AKTIER</t>
+  </si>
+  <si>
+    <t>WEBN</t>
+  </si>
+  <si>
+    <t>AmPrimeAllCntryWldUCITSETFUSDA</t>
+  </si>
+  <si>
+    <t>F_PASI</t>
+  </si>
+  <si>
+    <t>PLUS Allabolag Sverige Index</t>
+  </si>
+  <si>
+    <t>STATSOBLIGATIONER</t>
+  </si>
+  <si>
+    <t>F_CIBA</t>
+  </si>
+  <si>
+    <t>Captor Iris Bond A</t>
+  </si>
+  <si>
+    <t>RÅVARA</t>
+  </si>
+  <si>
+    <t>EN4C</t>
+  </si>
+  <si>
+    <t>L&amp;GMltStrgEnhCommsUCITSETFUSDA</t>
+  </si>
+  <si>
+    <t>GULD</t>
+  </si>
+  <si>
     <t>4GLD</t>
   </si>
   <si>
+    <t>DT BOERSE COMMOD GOLD ETC</t>
+  </si>
+  <si>
+    <t>AW Mellan</t>
+  </si>
+  <si>
+    <t>weekly</t>
+  </si>
+  <si>
+    <t>__rb_type</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>F_SSA</t>
+  </si>
+  <si>
+    <t>Storebrand Sverige A SEK</t>
+  </si>
+  <si>
+    <t>F_SSVFA</t>
+  </si>
+  <si>
+    <t>SEB Swedish Value Fund A</t>
+  </si>
+  <si>
+    <t>AVEM</t>
+  </si>
+  <si>
+    <t>Avantis EM Eq UCITS ETF USDA</t>
+  </si>
+  <si>
+    <t>XDEM</t>
+  </si>
+  <si>
+    <t>X MSCI Wld Mmntm UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>F_CAGCA</t>
+  </si>
+  <si>
+    <t>Captor Aster Global Credit A</t>
+  </si>
+  <si>
+    <t>REALRÄNTA</t>
+  </si>
+  <si>
+    <t>F_SRR</t>
+  </si>
+  <si>
+    <t>Swedbank Robur Realranta</t>
+  </si>
+  <si>
+    <t>LÅNG VOLATILITET</t>
+  </si>
+  <si>
+    <t>F_AFVW</t>
+  </si>
+  <si>
+    <t>Amundi Funds Volatility World - A USD (C)</t>
+  </si>
+  <si>
+    <t>STIL - TREND</t>
+  </si>
+  <si>
+    <t>F_LD</t>
+  </si>
+  <si>
+    <t>Lynx Dynamic</t>
+  </si>
+  <si>
+    <t>F_MMFHS</t>
+  </si>
+  <si>
+    <t>Mandatum Managed Futures H SEK cap perf</t>
+  </si>
+  <si>
+    <t>STIL - CARRY</t>
+  </si>
+  <si>
+    <t>UBF6</t>
+  </si>
+  <si>
+    <t>UBSCMCIComCrExAgSFUCITSETFUSDa</t>
+  </si>
+  <si>
+    <t>STIL - MACRO</t>
+  </si>
+  <si>
+    <t>BHMG</t>
+  </si>
+  <si>
+    <t>BH MACRO LIMITED</t>
+  </si>
+  <si>
+    <t>AW Adv AZ</t>
+  </si>
+  <si>
+    <t>AW Adv NN</t>
+  </si>
+  <si>
+    <t>daily</t>
+  </si>
+  <si>
+    <t>AVWS</t>
+  </si>
+  <si>
+    <t>Avantis Gl SmCp Val UETF USDA</t>
+  </si>
+  <si>
+    <t>F_ADA</t>
+  </si>
+  <si>
+    <t>Aktiespararna Direktavkastning A</t>
+  </si>
+  <si>
+    <t>F_ASE</t>
+  </si>
+  <si>
+    <t>Aktiespararna Smabolag Edge</t>
+  </si>
+  <si>
+    <t>F_KICA</t>
+  </si>
+  <si>
+    <t>Kvartil Investmentbolag + Calc A</t>
+  </si>
+  <si>
+    <t>F_AEMA</t>
+  </si>
+  <si>
+    <t>Avanza Emerging Markets A</t>
+  </si>
+  <si>
+    <t>FÖRETAGSOBLIGATIONER</t>
+  </si>
+  <si>
     <t>IS04</t>
   </si>
   <si>
-    <t>DT BOERSE COMMOD GOLD ETC</t>
-  </si>
-  <si>
     <t>iShs $ Trs Bd 20+y ETF USDD</t>
   </si>
   <si>
-    <t>Storebrand Sverige A SEK</t>
+    <t>CEB1</t>
+  </si>
+  <si>
+    <t>iShs € Gvt Bd20yrTgtDurETFEURA</t>
+  </si>
+  <si>
+    <t>F_DIGRS</t>
+  </si>
+  <si>
+    <t>Danske Invest Globala Realrantor SEK h</t>
   </si>
   <si>
     <t>IAU</t>
@@ -66,112 +290,34 @@
     <t>IShares:Gold Trust</t>
   </si>
   <si>
+    <t>GLDA</t>
+  </si>
+  <si>
+    <t>AMND GOLD LBMA ETF</t>
+  </si>
+  <si>
+    <t>8PSG</t>
+  </si>
+  <si>
+    <t>INVESCO PHYSICAL GOLD ETC</t>
+  </si>
+  <si>
     <t>GZUR</t>
   </si>
   <si>
     <t>WT Physical Swiss Gold</t>
   </si>
   <si>
-    <t>WEBN</t>
-  </si>
-  <si>
-    <t>AmPrimeAllCntryWldUCITSETFUSDA</t>
-  </si>
-  <si>
-    <t>PLUS Allabolag Sverige Index</t>
-  </si>
-  <si>
-    <t>Captor Iris Bond A</t>
-  </si>
-  <si>
-    <t>EN4C</t>
-  </si>
-  <si>
-    <t>L&amp;GMltStrgEnhCommsUCITSETFUSDA</t>
-  </si>
-  <si>
-    <t>_Name</t>
-  </si>
-  <si>
-    <t>Mandatum Managed Futures H SEK cap perf</t>
-  </si>
-  <si>
-    <t>AKTIER</t>
-  </si>
-  <si>
-    <t>GULD</t>
-  </si>
-  <si>
-    <t>RÅVARA</t>
-  </si>
-  <si>
-    <t>AVWS</t>
-  </si>
-  <si>
-    <t>Avantis Gl SmCp Val UETF USDA</t>
-  </si>
-  <si>
-    <t>Aktiespararna Direktavkastning A</t>
-  </si>
-  <si>
-    <t>SEB Swedish Value Fund A</t>
-  </si>
-  <si>
-    <t>AVEM</t>
-  </si>
-  <si>
-    <t>Avantis EM Eq UCITS ETF USDA</t>
-  </si>
-  <si>
-    <t>XDEM</t>
-  </si>
-  <si>
-    <t>X MSCI Wld Mmntm UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>Aktiespararna Smabolag Edge</t>
-  </si>
-  <si>
-    <t>Kvartil Investmentbolag + Calc A</t>
-  </si>
-  <si>
-    <t>Captor Aster Global Credit A</t>
-  </si>
-  <si>
-    <t>CEB1</t>
-  </si>
-  <si>
-    <t>iShs € Gvt Bd20yrTgtDurETFEURA</t>
-  </si>
-  <si>
-    <t>Swedbank Robur Realranta</t>
-  </si>
-  <si>
-    <t>Danske Invest Globala Realrantor SEK h</t>
-  </si>
-  <si>
-    <t>LÅNG VOLATILITET</t>
-  </si>
-  <si>
-    <t>Amundi Funds Volatility World - A USD (C)</t>
-  </si>
-  <si>
-    <t>Lynx Dynamic</t>
-  </si>
-  <si>
-    <t>UBF6</t>
-  </si>
-  <si>
-    <t>UBSCMCIComCrExAgSFUCITSETFUSDa</t>
-  </si>
-  <si>
-    <t>Avanza Emerging Markets A</t>
-  </si>
-  <si>
-    <t>BHMG</t>
-  </si>
-  <si>
-    <t>BH MACRO LIMITED</t>
+    <t>_XDEV</t>
+  </si>
+  <si>
+    <t>_MSCI_705130</t>
+  </si>
+  <si>
+    <t>OMXSCAPGI</t>
+  </si>
+  <si>
+    <t>yearly</t>
   </si>
   <si>
     <t>XDEV</t>
@@ -180,175 +326,28 @@
     <t>X MSCI Wld Value UCITS ETF 1C</t>
   </si>
   <si>
-    <t>REALRÄNTA</t>
-  </si>
-  <si>
-    <t>STATSOBLIGATIONER</t>
-  </si>
-  <si>
-    <t>FÖRETAGSOBLIGATIONER</t>
-  </si>
-  <si>
-    <t>GLDA</t>
-  </si>
-  <si>
-    <t>AMND GOLD LBMA ETF</t>
-  </si>
-  <si>
-    <t>8PSG</t>
-  </si>
-  <si>
-    <t>INVESCO PHYSICAL GOLD ETC</t>
-  </si>
-  <si>
-    <t>STIL - TREND</t>
-  </si>
-  <si>
-    <t>STIL - MACRO</t>
-  </si>
-  <si>
-    <t>STIL - CARRY</t>
-  </si>
-  <si>
-    <t>half-year</t>
-  </si>
-  <si>
-    <t>OMXSCAPGI</t>
+    <t>MSCI_705130</t>
+  </si>
+  <si>
+    <t>MSCI World Enhanced Value Index (USD) Index</t>
   </si>
   <si>
     <t>OMX Stockholm PI GI</t>
   </si>
   <si>
-    <t>MSCI_705130</t>
-  </si>
-  <si>
-    <t>MSCI World Enhanced Value Index (USD) Index</t>
-  </si>
-  <si>
-    <t>__rb_type</t>
-  </si>
-  <si>
-    <t>yearly</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>daily</t>
-  </si>
-  <si>
-    <t>weekly</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>end</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>currency</t>
-  </si>
-  <si>
-    <t>SEK</t>
-  </si>
-  <si>
-    <t>AW Adv AZ</t>
-  </si>
-  <si>
-    <t>AW Adv NN</t>
-  </si>
-  <si>
-    <t>AW Grund</t>
-  </si>
-  <si>
-    <t>AW_Avancerad</t>
-  </si>
-  <si>
-    <t>AW_Grund</t>
-  </si>
-  <si>
-    <t>AW Mellan</t>
-  </si>
-  <si>
-    <t>AW_Mellan</t>
-  </si>
-  <si>
-    <t>Benchmarks</t>
-  </si>
-  <si>
-    <t>_XDEV</t>
-  </si>
-  <si>
-    <t>_MSCI_705130</t>
-  </si>
-  <si>
-    <t>F_PASI</t>
-  </si>
-  <si>
-    <t>F_CIBA</t>
-  </si>
-  <si>
-    <t>F_SSA</t>
-  </si>
-  <si>
-    <t>F_CAGCA</t>
-  </si>
-  <si>
-    <t>F_SRR</t>
-  </si>
-  <si>
-    <t>F_AFVW</t>
-  </si>
-  <si>
-    <t>F_LD</t>
-  </si>
-  <si>
-    <t>F_MMFHS</t>
-  </si>
-  <si>
-    <t>F_ADA</t>
-  </si>
-  <si>
-    <t>F_SSVFA</t>
-  </si>
-  <si>
-    <t>F_ASE</t>
-  </si>
-  <si>
-    <t>F_KICA</t>
-  </si>
-  <si>
-    <t>F_AEMA</t>
-  </si>
-  <si>
-    <t>F_DIGRS</t>
-  </si>
-  <si>
-    <t>portfolios</t>
-  </si>
-  <si>
-    <t>assets</t>
-  </si>
-  <si>
-    <t>assets.xlsx!Assets</t>
-  </si>
-  <si>
-    <t>indices.xlsx!Assets</t>
-  </si>
-  <si>
-    <t>currencies.xlsx!Assets</t>
-  </si>
-  <si>
-    <t>__rb_check</t>
-  </si>
-  <si>
-    <t>_portfolios</t>
+    <t>borrow_rate_asset</t>
+  </si>
+  <si>
+    <t>STIBOR</t>
+  </si>
+  <si>
+    <t>borrow_rate_premium</t>
+  </si>
+  <si>
+    <t>__leverage</t>
+  </si>
+  <si>
+    <t>AW Grund (1,37)</t>
   </si>
 </sst>
 </file>
@@ -416,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -424,6 +423,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,33 +703,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4A2CED-8EDE-43DD-BA1E-B509AEA1C295}">
-  <dimension ref="A1:B11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="B3" s="6">
         <v>36892</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="B4" s="6">
         <v>46113</v>
@@ -745,58 +745,74 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="2">
+        <v>4.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -805,107 +821,139 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC042A6-C428-4DFB-B9A0-C13B28FBEDA1}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.84375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.07421875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.921875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>18</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
+        <v>20</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B6" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2">
+      <c r="D6" s="2">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="D8" s="2">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="D10" s="2">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.27</v>
+      </c>
+      <c r="D12" s="2">
         <v>0.27</v>
       </c>
     </row>
@@ -915,7 +963,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38B8714-1F9F-4582-A22F-F85A531C4EEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -926,44 +974,44 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2">
         <v>0.08</v>
@@ -971,10 +1019,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2">
         <v>0.04</v>
@@ -982,10 +1030,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>0.04</v>
@@ -993,10 +1041,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2">
         <v>0.04</v>
@@ -1004,10 +1052,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2">
         <v>0.1</v>
@@ -1015,15 +1063,15 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2">
         <v>0.1</v>
@@ -1031,15 +1079,15 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2">
         <v>0.08</v>
@@ -1047,15 +1095,15 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2">
         <v>0.1</v>
@@ -1063,15 +1111,15 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2">
         <v>0.18</v>
@@ -1079,28 +1127,28 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2">
         <v>0.08</v>
@@ -1108,23 +1156,23 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>0.08</v>
@@ -1132,15 +1180,15 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2">
         <v>0.08</v>
@@ -1152,7 +1200,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E3438D-7A90-4AFB-88E5-763ED78FEB57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1164,53 +1212,53 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2">
         <v>3.5000000000000003E-2</v>
@@ -1221,10 +1269,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>0.02</v>
@@ -1235,10 +1283,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2">
         <v>0.02</v>
@@ -1249,10 +1297,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2">
         <v>3.5000000000000003E-2</v>
@@ -1263,10 +1311,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2">
         <v>0.02</v>
@@ -1277,10 +1325,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C10" s="2">
         <v>0.02</v>
@@ -1291,10 +1339,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2">
         <v>0.06</v>
@@ -1302,10 +1350,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2">
         <v>0.06</v>
@@ -1313,15 +1361,15 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2">
         <v>9.5000000000000001E-2</v>
@@ -1332,15 +1380,15 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C16" s="2">
         <v>5.5E-2</v>
@@ -1351,10 +1399,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="C17" s="2">
         <v>0.02</v>
@@ -1365,10 +1413,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2">
         <v>0.02</v>
@@ -1379,15 +1427,15 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2">
         <v>7.4999999999999997E-2</v>
@@ -1398,15 +1446,15 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2">
         <v>5.5E-2</v>
@@ -1417,10 +1465,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C23" s="2">
         <v>0.04</v>
@@ -1431,23 +1479,23 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B24" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2">
         <v>0.08</v>
@@ -1458,10 +1506,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C27" s="2">
         <v>0.08</v>
@@ -1472,10 +1520,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C28" s="2">
         <v>0.03</v>
@@ -1483,10 +1531,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="D29" s="2">
         <v>0.08</v>
@@ -1494,15 +1542,15 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C31" s="2">
         <v>0.04</v>
@@ -1510,15 +1558,15 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B32" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2">
         <v>0.12</v>
@@ -1526,10 +1574,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="D34" s="2">
         <v>0.08</v>
@@ -1537,15 +1585,15 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>0.08</v>
@@ -1556,15 +1604,15 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D38" s="2">
         <v>0.08</v>
@@ -1576,7 +1624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CD033A-2741-413F-8268-615C5C585FBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1589,42 +1637,42 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -1634,10 +1682,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1645,10 +1693,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
